--- a/combined_sys_outputs.xlsx
+++ b/combined_sys_outputs.xlsx
@@ -474,10 +474,10 @@
         <v>101325</v>
       </c>
       <c r="E2" t="n">
-        <v>164511.7079079717</v>
+        <v>164510.1197280189</v>
       </c>
       <c r="F2" t="n">
-        <v>2963724.481240325</v>
+        <v>2963695.869733785</v>
       </c>
     </row>
     <row r="3">
@@ -494,10 +494,10 @@
         <v>101325</v>
       </c>
       <c r="E3" t="n">
-        <v>164511.7079079717</v>
+        <v>164510.1197280189</v>
       </c>
       <c r="F3" t="n">
-        <v>2963724.481240325</v>
+        <v>2963695.869733785</v>
       </c>
     </row>
     <row r="4">
@@ -514,10 +514,10 @@
         <v>101325</v>
       </c>
       <c r="E4" t="n">
-        <v>28678.13284471162</v>
+        <v>28678.14057133265</v>
       </c>
       <c r="F4" t="n">
-        <v>516644.5930746763</v>
+        <v>516644.7322719177</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>341.4809929900889</v>
+        <v>341.4809929900754</v>
       </c>
       <c r="D5" t="n">
         <v>101325</v>
       </c>
       <c r="E5" t="n">
-        <v>13338.90424583909</v>
+        <v>13338.90424567278</v>
       </c>
       <c r="F5" t="n">
-        <v>408691.7805718319</v>
+        <v>408691.7805666322</v>
       </c>
     </row>
     <row r="6">
@@ -682,10 +682,10 @@
         <v>101325</v>
       </c>
       <c r="E11" t="n">
-        <v>1.137193350623517</v>
+        <v>1.137193348274803</v>
       </c>
       <c r="F11" t="n">
-        <v>150.173457566863</v>
+        <v>150.1734572567007</v>
       </c>
     </row>
     <row r="12">
@@ -706,10 +706,10 @@
         <v>101325</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1775074160317971</v>
+        <v>0.1775074155156209</v>
       </c>
       <c r="F12" t="n">
-        <v>23.44095873814136</v>
+        <v>23.44095866997707</v>
       </c>
     </row>
     <row r="13">
@@ -730,10 +730,10 @@
         <v>101325</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9596859345821168</v>
+        <v>0.9596859321672412</v>
       </c>
       <c r="F13" t="n">
-        <v>126.7324988274535</v>
+        <v>126.7324985085541</v>
       </c>
     </row>
     <row r="14">
@@ -754,10 +754,10 @@
         <v>101325</v>
       </c>
       <c r="E14" t="n">
-        <v>5.002727985208223</v>
+        <v>5.002727707852156</v>
       </c>
       <c r="F14" t="n">
-        <v>146.2335410809051</v>
+        <v>146.2335329735765</v>
       </c>
     </row>
     <row r="15">
@@ -778,10 +778,10 @@
         <v>3000000</v>
       </c>
       <c r="E15" t="n">
-        <v>770.6399893248052</v>
+        <v>770.6399893248084</v>
       </c>
       <c r="F15" t="n">
-        <v>1553.517741680088</v>
+        <v>1553.517741680095</v>
       </c>
     </row>
     <row r="16">
@@ -802,10 +802,10 @@
         <v>101325</v>
       </c>
       <c r="E16" t="n">
-        <v>2334.106817334411</v>
+        <v>2334.106815978518</v>
       </c>
       <c r="F16" t="n">
-        <v>43085.54341801469</v>
+        <v>43085.5433674134</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>309.6293643827382</v>
+        <v>309.6277208384676</v>
       </c>
       <c r="D17" t="n">
         <v>101325</v>
       </c>
       <c r="E17" t="n">
-        <v>13495.4241398555</v>
+        <v>13495.42413986945</v>
       </c>
       <c r="F17" t="n">
-        <v>413522.4854639735</v>
+        <v>413522.4854643174</v>
       </c>
     </row>
     <row r="18">
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>503.6754216675718</v>
+        <v>503.6754212072045</v>
       </c>
       <c r="D19" t="n">
         <v>101326</v>
       </c>
       <c r="E19" t="n">
-        <v>345.4219980178439</v>
+        <v>345.4220000850685</v>
       </c>
       <c r="F19" t="n">
-        <v>2626.163201612593</v>
+        <v>2626.163234738091</v>
       </c>
     </row>
     <row r="20">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>408.7058857883466</v>
+        <v>408.7058857881768</v>
       </c>
       <c r="D22" t="n">
         <v>101325</v>
       </c>
       <c r="E22" t="n">
-        <v>2316.808085018028</v>
+        <v>2316.808085019819</v>
       </c>
       <c r="F22" t="n">
-        <v>43890.5235925298</v>
+        <v>43890.5235925571</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D23" t="n">
         <v>101325</v>
       </c>
       <c r="E23" t="n">
-        <v>19613.71562825187</v>
+        <v>19613.7269109447</v>
       </c>
       <c r="F23" t="n">
-        <v>353346.5788833334</v>
+        <v>353346.7821442038</v>
       </c>
     </row>
     <row r="24">
@@ -994,10 +994,10 @@
         <v>6000000</v>
       </c>
       <c r="E24" t="n">
-        <v>16060.32138343267</v>
+        <v>16060.32138551564</v>
       </c>
       <c r="F24" t="n">
-        <v>484351.487849785</v>
+        <v>484351.4878832817</v>
       </c>
     </row>
     <row r="25">
@@ -1018,10 +1018,10 @@
         <v>101325</v>
       </c>
       <c r="E25" t="n">
-        <v>173.0977606050617</v>
+        <v>173.097760604383</v>
       </c>
       <c r="F25" t="n">
-        <v>5240.912934977182</v>
+        <v>5240.91293495995</v>
       </c>
     </row>
     <row r="26">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>372.9275880574507</v>
+        <v>372.9275880574508</v>
       </c>
       <c r="D26" t="n">
         <v>101325</v>
       </c>
       <c r="E26" t="n">
-        <v>2143.710324412966</v>
+        <v>2143.710324415436</v>
       </c>
       <c r="F26" t="n">
-        <v>38649.61065755263</v>
+        <v>38649.61065759715</v>
       </c>
     </row>
     <row r="27">
@@ -1066,10 +1066,10 @@
         <v>101325</v>
       </c>
       <c r="E27" t="n">
-        <v>84882.75664219704</v>
+        <v>80052.18826485172</v>
       </c>
       <c r="F27" t="n">
-        <v>2441718.164500124</v>
+        <v>2302763.127948442</v>
       </c>
     </row>
     <row r="28">
@@ -1090,10 +1090,10 @@
         <v>101325</v>
       </c>
       <c r="E28" t="n">
-        <v>121.0282858684431</v>
+        <v>121.0281230389318</v>
       </c>
       <c r="F28" t="n">
-        <v>3485.930555214919</v>
+        <v>3485.925865299956</v>
       </c>
     </row>
     <row r="29">
@@ -1162,10 +1162,10 @@
         <v>101325</v>
       </c>
       <c r="E31" t="n">
-        <v>1035.865013430954</v>
+        <v>1035.761562069048</v>
       </c>
       <c r="F31" t="n">
-        <v>1457.123344369384</v>
+        <v>1456.991053111686</v>
       </c>
     </row>
     <row r="32">
@@ -1180,16 +1180,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>304.6565436477393</v>
+        <v>304.6565436414825</v>
       </c>
       <c r="D32" t="n">
         <v>101325</v>
       </c>
       <c r="E32" t="n">
-        <v>21405.76188574149</v>
+        <v>21405.76158266707</v>
       </c>
       <c r="F32" t="n">
-        <v>398534.4134550694</v>
+        <v>398534.4134983607</v>
       </c>
     </row>
     <row r="33">
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>307.9988284447388</v>
+        <v>307.9988281640277</v>
       </c>
       <c r="D33" t="n">
         <v>101325</v>
       </c>
       <c r="E33" t="n">
-        <v>231.1199857811356</v>
+        <v>231.1197271659634</v>
       </c>
       <c r="F33" t="n">
-        <v>6735.782099330527</v>
+        <v>6735.774568927714</v>
       </c>
     </row>
     <row r="34">
@@ -1234,10 +1234,10 @@
         <v>101325</v>
       </c>
       <c r="E34" t="n">
-        <v>1385.151951304734</v>
+        <v>1297.630662535305</v>
       </c>
       <c r="F34" t="n">
-        <v>24953.90024530115</v>
+        <v>23377.17972215903</v>
       </c>
     </row>
     <row r="35">
@@ -1258,10 +1258,10 @@
         <v>101325</v>
       </c>
       <c r="E35" t="n">
-        <v>1.609110667484502</v>
+        <v>1.507438472417221</v>
       </c>
       <c r="F35" t="n">
-        <v>1.609110667484502</v>
+        <v>1.507438472417221</v>
       </c>
     </row>
     <row r="36">
@@ -1276,16 +1276,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D36" t="n">
         <v>101325</v>
       </c>
       <c r="E36" t="n">
-        <v>387.5605489240154</v>
+        <v>387.5604578829542</v>
       </c>
       <c r="F36" t="n">
-        <v>11621.55518804603</v>
+        <v>11621.54829823617</v>
       </c>
     </row>
     <row r="37">
@@ -1306,10 +1306,10 @@
         <v>101325</v>
       </c>
       <c r="E37" t="n">
-        <v>180.8156060786935</v>
+        <v>180.8157032764728</v>
       </c>
       <c r="F37" t="n">
-        <v>4491.741742155215</v>
+        <v>4491.74415669969</v>
       </c>
     </row>
     <row r="38">
@@ -1354,10 +1354,10 @@
         <v>101325</v>
       </c>
       <c r="E39" t="n">
-        <v>164.5117079079717</v>
+        <v>164.5101197280189</v>
       </c>
       <c r="F39" t="n">
-        <v>2963.724481240325</v>
+        <v>2963.695869733785</v>
       </c>
     </row>
     <row r="40">
@@ -1378,10 +1378,10 @@
         <v>101325</v>
       </c>
       <c r="E40" t="n">
-        <v>0.04150812479688246</v>
+        <v>0.04150772408150166</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7477804904907805</v>
+        <v>0.7477732714909952</v>
       </c>
     </row>
     <row r="41">
@@ -1402,10 +1402,10 @@
         <v>101325</v>
       </c>
       <c r="E41" t="n">
-        <v>1645.117079079717</v>
+        <v>1645.101197280189</v>
       </c>
       <c r="F41" t="n">
-        <v>29637.24481240325</v>
+        <v>29636.95869733785</v>
       </c>
     </row>
     <row r="42">
@@ -1426,10 +1426,10 @@
         <v>101325</v>
       </c>
       <c r="E42" t="n">
-        <v>1809.628786987689</v>
+        <v>1809.611317008208</v>
       </c>
       <c r="F42" t="n">
-        <v>32600.96929364357</v>
+        <v>32600.65456707164</v>
       </c>
     </row>
     <row r="43">
@@ -1450,10 +1450,10 @@
         <v>101325</v>
       </c>
       <c r="E43" t="n">
-        <v>4.091109079984361</v>
+        <v>4.091109079982865</v>
       </c>
       <c r="F43" t="n">
-        <v>467.3213353651752</v>
+        <v>467.3213353650043</v>
       </c>
     </row>
     <row r="44">
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>467.4710041102428</v>
+        <v>466.3126854533675</v>
       </c>
       <c r="D44" t="n">
         <v>101325</v>
       </c>
       <c r="E44" t="n">
-        <v>88403.78014862655</v>
+        <v>83396.00423111911</v>
       </c>
       <c r="F44" t="n">
-        <v>2508794.145897162</v>
+        <v>2366996.264005919</v>
       </c>
     </row>
     <row r="45">
@@ -1492,16 +1492,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>339.2608347208658</v>
+        <v>339.2608347208638</v>
       </c>
       <c r="D45" t="n">
         <v>101325</v>
       </c>
       <c r="E45" t="n">
-        <v>471.5904742300903</v>
+        <v>471.5904742275866</v>
       </c>
       <c r="F45" t="n">
-        <v>21709.84735467306</v>
+        <v>21709.84735466513</v>
       </c>
     </row>
     <row r="46">
@@ -1522,10 +1522,10 @@
         <v>101325</v>
       </c>
       <c r="E46" t="n">
-        <v>1682.489550101557</v>
+        <v>1682.490285830715</v>
       </c>
       <c r="F46" t="n">
-        <v>31836.94089113107</v>
+        <v>31836.95206634208</v>
       </c>
     </row>
     <row r="47">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>414.4311859428768</v>
+        <v>414.4312778935794</v>
       </c>
       <c r="D48" t="n">
         <v>101325</v>
       </c>
       <c r="E48" t="n">
-        <v>576.5414719619732</v>
+        <v>576.5417272427495</v>
       </c>
       <c r="F48" t="n">
-        <v>9361.937099195469</v>
+        <v>9361.937803533088</v>
       </c>
     </row>
     <row r="49">
@@ -1588,16 +1588,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>591.5069269534928</v>
+        <v>591.5069269534905</v>
       </c>
       <c r="D49" t="n">
         <v>3000000</v>
       </c>
       <c r="E49" t="n">
-        <v>1459.903082022032</v>
+        <v>1459.903082022031</v>
       </c>
       <c r="F49" t="n">
-        <v>2942.989424986574</v>
+        <v>2942.989424986572</v>
       </c>
     </row>
     <row r="50">
@@ -1642,10 +1642,10 @@
         <v>101325</v>
       </c>
       <c r="E51" t="n">
-        <v>1956.453553745068</v>
+        <v>1956.366762979018</v>
       </c>
       <c r="F51" t="n">
-        <v>35246.05857771246</v>
+        <v>35244.49501776064</v>
       </c>
     </row>
     <row r="52">
@@ -1666,10 +1666,10 @@
         <v>101325</v>
       </c>
       <c r="E52" t="n">
-        <v>1385.151951304734</v>
+        <v>1297.630662535305</v>
       </c>
       <c r="F52" t="n">
-        <v>24953.90024530115</v>
+        <v>23377.17972215903</v>
       </c>
     </row>
     <row r="53">
@@ -1690,10 +1690,10 @@
         <v>101559.77492837</v>
       </c>
       <c r="E53" t="n">
-        <v>2262.101611637359</v>
+        <v>2084.892227896808</v>
       </c>
       <c r="F53" t="n">
-        <v>36289.67462062787</v>
+        <v>33446.80017034543</v>
       </c>
     </row>
     <row r="54">
@@ -1732,16 +1732,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>374.4143912976353</v>
+        <v>374.4143830666779</v>
       </c>
       <c r="D55" t="n">
         <v>101325</v>
       </c>
       <c r="E55" t="n">
-        <v>12173.15975989752</v>
+        <v>12173.22451274574</v>
       </c>
       <c r="F55" t="n">
-        <v>253226.8664534772</v>
+        <v>253228.0391975455</v>
       </c>
     </row>
     <row r="56">
@@ -1786,10 +1786,10 @@
         <v>101325</v>
       </c>
       <c r="E57" t="n">
-        <v>1001.897150773582</v>
+        <v>1001.832397925357</v>
       </c>
       <c r="F57" t="n">
-        <v>18201.33239063077</v>
+        <v>18200.15964656246</v>
       </c>
     </row>
     <row r="58">
@@ -1810,10 +1810,10 @@
         <v>101325</v>
       </c>
       <c r="E58" t="n">
-        <v>28678.13284471162</v>
+        <v>28678.14057133265</v>
       </c>
       <c r="F58" t="n">
-        <v>516644.5930746763</v>
+        <v>516644.7322719177</v>
       </c>
     </row>
     <row r="59">
@@ -1828,16 +1828,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>386.84602910017</v>
+        <v>386.8460291001701</v>
       </c>
       <c r="D59" t="n">
         <v>162120</v>
       </c>
       <c r="E59" t="n">
-        <v>1165.518200772243</v>
+        <v>1165.518200775619</v>
       </c>
       <c r="F59" t="n">
-        <v>20997.26459481816</v>
+        <v>20997.26459487898</v>
       </c>
     </row>
     <row r="60">
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>308.0662892590592</v>
+        <v>308.0602187379017</v>
       </c>
       <c r="D60" t="n">
         <v>101325</v>
       </c>
       <c r="E60" t="n">
-        <v>15829.53095373661</v>
+        <v>15829.53095584791</v>
       </c>
       <c r="F60" t="n">
-        <v>456608.0287968341</v>
+        <v>456608.0288317293</v>
       </c>
     </row>
     <row r="61">
@@ -1882,10 +1882,10 @@
         <v>500000</v>
       </c>
       <c r="E61" t="n">
-        <v>1805.325080039876</v>
+        <v>1805.3250821071</v>
       </c>
       <c r="F61" t="n">
-        <v>5569.152626599166</v>
+        <v>5569.152659724664</v>
       </c>
     </row>
     <row r="62">
@@ -1906,10 +1906,10 @@
         <v>500000</v>
       </c>
       <c r="E62" t="n">
-        <v>156.5198940164109</v>
+        <v>156.5198941966692</v>
       </c>
       <c r="F62" t="n">
-        <v>4830.704892141665</v>
+        <v>4830.704897685293</v>
       </c>
     </row>
     <row r="63">
@@ -1930,10 +1930,10 @@
         <v>500000</v>
       </c>
       <c r="E63" t="n">
-        <v>1805.325080039876</v>
+        <v>1805.3250821071</v>
       </c>
       <c r="F63" t="n">
-        <v>5569.152626599166</v>
+        <v>5569.152659724664</v>
       </c>
     </row>
     <row r="64">
@@ -1954,10 +1954,10 @@
         <v>500000</v>
       </c>
       <c r="E64" t="n">
-        <v>1459.903082022032</v>
+        <v>1459.903082022031</v>
       </c>
       <c r="F64" t="n">
-        <v>2942.989424986574</v>
+        <v>2942.989424986572</v>
       </c>
     </row>
     <row r="65">
@@ -1972,16 +1972,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>346.6531218135032</v>
+        <v>346.6531218135567</v>
       </c>
       <c r="D65" t="n">
         <v>101325</v>
       </c>
       <c r="E65" t="n">
-        <v>15482.61457025206</v>
+        <v>15482.61457008822</v>
       </c>
       <c r="F65" t="n">
-        <v>447341.3912293845</v>
+        <v>447341.3912242293</v>
       </c>
     </row>
     <row r="66">
@@ -1996,16 +1996,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>369.7889814436428</v>
+        <v>369.7889814436717</v>
       </c>
       <c r="D66" t="n">
         <v>101325</v>
       </c>
       <c r="E66" t="n">
-        <v>288.1596216392326</v>
+        <v>288.159621638554</v>
       </c>
       <c r="F66" t="n">
-        <v>30072.57960164385</v>
+        <v>30072.57960162662</v>
       </c>
     </row>
     <row r="67">
@@ -2020,16 +2020,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>341.4003076138707</v>
+        <v>341.4003076137647</v>
       </c>
       <c r="D67" t="n">
         <v>101325</v>
       </c>
       <c r="E67" t="n">
-        <v>13495.4241398555</v>
+        <v>13495.42413986945</v>
       </c>
       <c r="F67" t="n">
-        <v>413522.4854639735</v>
+        <v>413522.4854643174</v>
       </c>
     </row>
     <row r="68">
@@ -2068,16 +2068,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>308.0662892590592</v>
+        <v>308.0602187379017</v>
       </c>
       <c r="D69" t="n">
         <v>6000000</v>
       </c>
       <c r="E69" t="n">
-        <v>15829.53095373661</v>
+        <v>15829.53095584791</v>
       </c>
       <c r="F69" t="n">
-        <v>456608.0287968341</v>
+        <v>456608.0288317293</v>
       </c>
     </row>
     <row r="70">
@@ -2194,10 +2194,10 @@
         <v>6000000</v>
       </c>
       <c r="E74" t="n">
-        <v>15829.53095373661</v>
+        <v>15829.53095584791</v>
       </c>
       <c r="F74" t="n">
-        <v>456608.0287968341</v>
+        <v>456608.0288317293</v>
       </c>
     </row>
     <row r="75">
@@ -2239,13 +2239,13 @@
         <v>403.15</v>
       </c>
       <c r="D76" t="n">
-        <v>270005.8303109665</v>
+        <v>270005.8511533333</v>
       </c>
       <c r="E76" t="n">
-        <v>488.6982926977322</v>
+        <v>488.6296371669989</v>
       </c>
       <c r="F76" t="n">
-        <v>8885.064836644213</v>
+        <v>8883.819055929433</v>
       </c>
     </row>
     <row r="77">
@@ -2263,13 +2263,13 @@
         <v>403.15</v>
       </c>
       <c r="D77" t="n">
-        <v>270005.8303109665</v>
+        <v>270005.8511533333</v>
       </c>
       <c r="E77" t="n">
-        <v>9350.840501484157</v>
+        <v>9350.90915701489</v>
       </c>
       <c r="F77" t="n">
-        <v>202036.8648547117</v>
+        <v>202038.1106354265</v>
       </c>
     </row>
     <row r="78">
@@ -2287,13 +2287,13 @@
         <v>403.15</v>
       </c>
       <c r="D78" t="n">
-        <v>270005.8303109665</v>
+        <v>270005.8511533333</v>
       </c>
       <c r="E78" t="n">
-        <v>9350.840501484157</v>
+        <v>9350.90915701489</v>
       </c>
       <c r="F78" t="n">
-        <v>202036.8648547117</v>
+        <v>202038.1106354265</v>
       </c>
     </row>
     <row r="79">
@@ -2311,13 +2311,13 @@
         <v>403.15</v>
       </c>
       <c r="D79" t="n">
-        <v>270005.8303109665</v>
+        <v>270005.8511533333</v>
       </c>
       <c r="E79" t="n">
-        <v>9350.840501484157</v>
+        <v>9350.90915701489</v>
       </c>
       <c r="F79" t="n">
-        <v>202036.8648547117</v>
+        <v>202038.1106354265</v>
       </c>
     </row>
     <row r="80">
@@ -2332,16 +2332,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>373.1653842329353</v>
+        <v>373.1653822092472</v>
       </c>
       <c r="D80" t="n">
         <v>101325</v>
       </c>
       <c r="E80" t="n">
-        <v>513.1988580758492</v>
+        <v>513.2027607583581</v>
       </c>
       <c r="F80" t="n">
-        <v>9316.26755398656</v>
+        <v>9316.340590633021</v>
       </c>
     </row>
     <row r="81">
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>373.1653842329353</v>
+        <v>373.1653822092472</v>
       </c>
       <c r="D81" t="n">
         <v>101325</v>
       </c>
       <c r="E81" t="n">
-        <v>8837.641643408308</v>
+        <v>8837.706396256532</v>
       </c>
       <c r="F81" t="n">
-        <v>192720.5973007251</v>
+        <v>192721.7700447934</v>
       </c>
     </row>
     <row r="82">
@@ -2380,16 +2380,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>387.8261223896698</v>
+        <v>387.8250118992472</v>
       </c>
       <c r="D82" t="n">
         <v>101325</v>
       </c>
       <c r="E82" t="n">
-        <v>1001.897150773582</v>
+        <v>1001.832397925357</v>
       </c>
       <c r="F82" t="n">
-        <v>18201.33239063077</v>
+        <v>18200.15964656246</v>
       </c>
     </row>
     <row r="83">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>509.3098039310902</v>
+        <v>509.3098039310901</v>
       </c>
       <c r="D85" t="n">
         <v>3000000</v>
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>374.4143912976353</v>
+        <v>374.4143830666779</v>
       </c>
       <c r="D86" t="n">
         <v>101325</v>
       </c>
       <c r="E86" t="n">
-        <v>12173.15975989752</v>
+        <v>12173.22451274574</v>
       </c>
       <c r="F86" t="n">
-        <v>253226.8664534772</v>
+        <v>253228.0391975455</v>
       </c>
     </row>
     <row r="87">
@@ -2500,13 +2500,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>344.7167153665706</v>
+        <v>344.7169632287188</v>
       </c>
       <c r="D87" t="n">
         <v>101325</v>
       </c>
       <c r="E87" t="n">
-        <v>19819.25267196402</v>
+        <v>19819.25232762429</v>
       </c>
       <c r="F87" t="n">
         <v>391160.1294498382</v>
@@ -2530,7 +2530,7 @@
         <v>101325</v>
       </c>
       <c r="E88" t="n">
-        <v>19819.25267196402</v>
+        <v>19819.25232762429</v>
       </c>
       <c r="F88" t="n">
         <v>391160.1294498382</v>
@@ -2554,10 +2554,10 @@
         <v>101325</v>
       </c>
       <c r="E89" t="n">
-        <v>1.137193350623517</v>
+        <v>1.137193348274803</v>
       </c>
       <c r="F89" t="n">
-        <v>150.173457566863</v>
+        <v>150.1734572567007</v>
       </c>
     </row>
     <row r="90">
@@ -2602,7 +2602,7 @@
         <v>101325</v>
       </c>
       <c r="E91" t="n">
-        <v>1964.406427374668</v>
+        <v>1964.406392940694</v>
       </c>
       <c r="F91" t="n">
         <v>39116.01294498384</v>
@@ -2650,10 +2650,10 @@
         <v>101325</v>
       </c>
       <c r="E93" t="n">
-        <v>1998.223317643819</v>
+        <v>1998.22328320933</v>
       </c>
       <c r="F93" t="n">
-        <v>37388.16880341986</v>
+        <v>37388.16880335171</v>
       </c>
     </row>
     <row r="94">
@@ -2674,10 +2674,10 @@
         <v>101325</v>
       </c>
       <c r="E94" t="n">
-        <v>1998.223317643819</v>
+        <v>1998.22328320933</v>
       </c>
       <c r="F94" t="n">
-        <v>37388.16880341986</v>
+        <v>37388.16880335171</v>
       </c>
     </row>
     <row r="95">
@@ -2698,10 +2698,10 @@
         <v>101325</v>
       </c>
       <c r="E95" t="n">
-        <v>435.8808291842851</v>
+        <v>435.8808294291437</v>
       </c>
       <c r="F95" t="n">
-        <v>18685.92619483898</v>
+        <v>18685.92622933755</v>
       </c>
     </row>
     <row r="96">
@@ -2746,10 +2746,10 @@
         <v>101325</v>
       </c>
       <c r="E97" t="n">
-        <v>19933.52267228795</v>
+        <v>19933.52236654863</v>
       </c>
       <c r="F97" t="n">
-        <v>371880.5333219533</v>
+        <v>371880.5332871447</v>
       </c>
     </row>
     <row r="98">
@@ -2764,16 +2764,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>304.6565436477393</v>
+        <v>304.6565436414825</v>
       </c>
       <c r="D98" t="n">
         <v>101325</v>
       </c>
       <c r="E98" t="n">
-        <v>21405.76188574149</v>
+        <v>21405.76158266707</v>
       </c>
       <c r="F98" t="n">
-        <v>398534.4134550694</v>
+        <v>398534.4134983607</v>
       </c>
     </row>
     <row r="99">
@@ -2788,16 +2788,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>304.5064465817767</v>
+        <v>304.5064465829527</v>
       </c>
       <c r="D99" t="n">
         <v>101325</v>
       </c>
       <c r="E99" t="n">
-        <v>480.3895082395111</v>
+        <v>480.3895084843697</v>
       </c>
       <c r="F99" t="n">
-        <v>20639.59231093881</v>
+        <v>20639.59234543738</v>
       </c>
     </row>
     <row r="100">
@@ -2818,10 +2818,10 @@
         <v>101325</v>
       </c>
       <c r="E100" t="n">
-        <v>1472.239213453533</v>
+        <v>1472.239216118432</v>
       </c>
       <c r="F100" t="n">
-        <v>26653.88013311598</v>
+        <v>26653.88021121594</v>
       </c>
     </row>
     <row r="101">
@@ -2836,16 +2836,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>386.1429167868738</v>
+        <v>386.1429167869409</v>
       </c>
       <c r="D101" t="n">
         <v>212782.5</v>
       </c>
       <c r="E101" t="n">
-        <v>1633.017565922359</v>
+        <v>1633.01756592385</v>
       </c>
       <c r="F101" t="n">
-        <v>42239.79061412636</v>
+        <v>42239.79061419786</v>
       </c>
     </row>
     <row r="102">
@@ -2860,16 +2860,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>304.6565436477393</v>
+        <v>304.6565436414825</v>
       </c>
       <c r="D102" t="n">
         <v>607950</v>
       </c>
       <c r="E102" t="n">
-        <v>21405.76188574149</v>
+        <v>21405.76158266707</v>
       </c>
       <c r="F102" t="n">
-        <v>398534.4134550694</v>
+        <v>398534.4134983607</v>
       </c>
     </row>
     <row r="103">
@@ -2884,16 +2884,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>395.3479493002509</v>
+        <v>395.3479487072207</v>
       </c>
       <c r="D103" t="n">
         <v>212782.5</v>
       </c>
       <c r="E103" t="n">
-        <v>19772.74431981914</v>
+        <v>19772.74401674323</v>
       </c>
       <c r="F103" t="n">
-        <v>356294.622840943</v>
+        <v>356294.6228841628</v>
       </c>
     </row>
     <row r="104">
@@ -2908,16 +2908,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>395.3479493002509</v>
+        <v>395.3479487072207</v>
       </c>
       <c r="D104" t="n">
         <v>607950</v>
       </c>
       <c r="E104" t="n">
-        <v>19772.74431981914</v>
+        <v>19772.74401674323</v>
       </c>
       <c r="F104" t="n">
-        <v>356294.622840943</v>
+        <v>356294.6228841628</v>
       </c>
     </row>
     <row r="105">
@@ -2932,16 +2932,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>377.9853644950165</v>
+        <v>377.9853654148564</v>
       </c>
       <c r="D105" t="n">
         <v>607950</v>
       </c>
       <c r="E105" t="n">
-        <v>21405.76188574149</v>
+        <v>21405.76158266707</v>
       </c>
       <c r="F105" t="n">
-        <v>398534.4134550694</v>
+        <v>398534.4134983607</v>
       </c>
     </row>
     <row r="106">
@@ -2956,16 +2956,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>386.3978152966313</v>
+        <v>386.3978152966897</v>
       </c>
       <c r="D106" t="n">
         <v>162120</v>
       </c>
       <c r="E106" t="n">
-        <v>1841.293540876779</v>
+        <v>1841.2935408782</v>
       </c>
       <c r="F106" t="n">
-        <v>48472.48733935459</v>
+        <v>48472.487339424</v>
       </c>
     </row>
     <row r="107">
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>456.0661336492133</v>
+        <v>456.0661336620269</v>
       </c>
       <c r="D107" t="n">
         <v>6000000</v>
       </c>
       <c r="E107" t="n">
-        <v>17732.61916594757</v>
+        <v>17732.61916803054</v>
       </c>
       <c r="F107" t="n">
-        <v>487813.8283497692</v>
+        <v>487813.8283832659</v>
       </c>
     </row>
     <row r="108">
@@ -3004,16 +3004,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>363.9172492735851</v>
+        <v>363.9172492737321</v>
       </c>
       <c r="D108" t="n">
         <v>162120</v>
       </c>
       <c r="E108" t="n">
-        <v>675.7753401045359</v>
+        <v>675.7753401025801</v>
       </c>
       <c r="F108" t="n">
-        <v>27475.22274453643</v>
+        <v>27475.22274454502</v>
       </c>
     </row>
     <row r="109">
@@ -3028,16 +3028,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>386.84602910017</v>
+        <v>386.8460291001701</v>
       </c>
       <c r="D109" t="n">
         <v>162120</v>
       </c>
       <c r="E109" t="n">
-        <v>1165.518200772243</v>
+        <v>1165.518200775619</v>
       </c>
       <c r="F109" t="n">
-        <v>20997.26459481816</v>
+        <v>20997.26459487898</v>
       </c>
     </row>
     <row r="110">
@@ -3058,10 +3058,10 @@
         <v>162120</v>
       </c>
       <c r="E110" t="n">
-        <v>675.7753401045359</v>
+        <v>675.7753401025801</v>
       </c>
       <c r="F110" t="n">
-        <v>27475.22274453643</v>
+        <v>27475.22274454502</v>
       </c>
     </row>
     <row r="111">
@@ -3082,10 +3082,10 @@
         <v>162120</v>
       </c>
       <c r="E111" t="n">
-        <v>208.2759749544298</v>
+        <v>208.2759749549763</v>
       </c>
       <c r="F111" t="n">
-        <v>6232.696725228536</v>
+        <v>6232.69672524489</v>
       </c>
     </row>
     <row r="112">
@@ -3106,10 +3106,10 @@
         <v>162120</v>
       </c>
       <c r="E112" t="n">
-        <v>467.499365150106</v>
+        <v>467.4993651476038</v>
       </c>
       <c r="F112" t="n">
-        <v>21242.52601930789</v>
+        <v>21242.52601930012</v>
       </c>
     </row>
     <row r="113">
@@ -3130,10 +3130,10 @@
         <v>162120</v>
       </c>
       <c r="E113" t="n">
-        <v>467.499365150106</v>
+        <v>467.4993651476038</v>
       </c>
       <c r="F113" t="n">
-        <v>21242.52601930789</v>
+        <v>21242.52601930012</v>
       </c>
     </row>
     <row r="114">
@@ -3154,10 +3154,10 @@
         <v>162120</v>
       </c>
       <c r="E114" t="n">
-        <v>467.499365150106</v>
+        <v>467.4993651476038</v>
       </c>
       <c r="F114" t="n">
-        <v>21242.52601930789</v>
+        <v>21242.52601930012</v>
       </c>
     </row>
     <row r="115">
@@ -3178,10 +3178,10 @@
         <v>162120</v>
       </c>
       <c r="E115" t="n">
-        <v>467.499365150106</v>
+        <v>467.4993651476038</v>
       </c>
       <c r="F115" t="n">
-        <v>21242.52601930789</v>
+        <v>21242.52601930012</v>
       </c>
     </row>
     <row r="116">
@@ -3202,10 +3202,10 @@
         <v>101325</v>
       </c>
       <c r="E116" t="n">
-        <v>4.091109079984361</v>
+        <v>4.091109079982865</v>
       </c>
       <c r="F116" t="n">
-        <v>467.3213353651752</v>
+        <v>467.3213353650043</v>
       </c>
     </row>
     <row r="117">
@@ -3226,10 +3226,10 @@
         <v>101325</v>
       </c>
       <c r="E117" t="n">
-        <v>4.091109079984361</v>
+        <v>4.091109079982865</v>
       </c>
       <c r="F117" t="n">
-        <v>467.3213353651752</v>
+        <v>467.3213353650043</v>
       </c>
     </row>
     <row r="118">
@@ -3250,10 +3250,10 @@
         <v>500000</v>
       </c>
       <c r="E118" t="n">
-        <v>1961.844974056286</v>
+        <v>1961.844976303769</v>
       </c>
       <c r="F118" t="n">
-        <v>10399.85751874083</v>
+        <v>10399.85755740996</v>
       </c>
     </row>
     <row r="119">
@@ -3268,16 +3268,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>339.2608347208658</v>
+        <v>339.2608347208638</v>
       </c>
       <c r="D119" t="n">
         <v>101325</v>
       </c>
       <c r="E119" t="n">
-        <v>471.5904742300903</v>
+        <v>471.5904742275866</v>
       </c>
       <c r="F119" t="n">
-        <v>21709.84735467306</v>
+        <v>21709.84735466513</v>
       </c>
     </row>
     <row r="120">
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>314.6565596550853</v>
+        <v>314.6565596488285</v>
       </c>
       <c r="D121" t="n">
         <v>395167.5</v>
       </c>
       <c r="E121" t="n">
-        <v>1478.061200068741</v>
+        <v>1478.061198819391</v>
       </c>
       <c r="F121" t="n">
-        <v>19711.20023485523</v>
+        <v>19711.20018715714</v>
       </c>
     </row>
     <row r="122">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>314.6565596550853</v>
+        <v>314.6565596488285</v>
       </c>
       <c r="D122" t="n">
         <v>395167.5</v>
       </c>
       <c r="E122" t="n">
-        <v>18294.738633829</v>
+        <v>18294.73867392791</v>
       </c>
       <c r="F122" t="n">
-        <v>336584.422605283</v>
+        <v>336584.422647441</v>
       </c>
     </row>
     <row r="123">
@@ -3364,16 +3364,16 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>327.636868326029</v>
+        <v>327.6367322910766</v>
       </c>
       <c r="D123" t="n">
         <v>101325</v>
       </c>
       <c r="E123" t="n">
-        <v>21613.44386962061</v>
+        <v>21613.37915687308</v>
       </c>
       <c r="F123" t="n">
-        <v>398676.2785884435</v>
+        <v>398675.1058865606</v>
       </c>
     </row>
     <row r="124">
@@ -3388,16 +3388,16 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>327.636868326029</v>
+        <v>327.6367322910766</v>
       </c>
       <c r="D124" t="n">
         <v>101325</v>
       </c>
       <c r="E124" t="n">
-        <v>21613.44386962061</v>
+        <v>21613.37915687308</v>
       </c>
       <c r="F124" t="n">
-        <v>398676.2785884435</v>
+        <v>398675.1058865606</v>
       </c>
     </row>
     <row r="125">
@@ -3412,16 +3412,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>307.9988284447388</v>
+        <v>307.9988281640277</v>
       </c>
       <c r="D125" t="n">
         <v>101325</v>
       </c>
       <c r="E125" t="n">
-        <v>19983.7790860043</v>
+        <v>19983.71904242638</v>
       </c>
       <c r="F125" t="n">
-        <v>363736.7249927613</v>
+        <v>363735.6426863864</v>
       </c>
     </row>
     <row r="126">
@@ -3442,10 +3442,10 @@
         <v>101325</v>
       </c>
       <c r="E126" t="n">
-        <v>1552.214044088159</v>
+        <v>1552.209450603593</v>
       </c>
       <c r="F126" t="n">
-        <v>28203.77149635163</v>
+        <v>28203.68863124657</v>
       </c>
     </row>
     <row r="127">
@@ -3460,16 +3460,16 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>308.0111724973675</v>
+        <v>308.0111725134954</v>
       </c>
       <c r="D127" t="n">
         <v>101325</v>
       </c>
       <c r="E127" t="n">
-        <v>119005.3490987921</v>
+        <v>119005.410395386</v>
       </c>
       <c r="F127" t="n">
-        <v>2173640.854085024</v>
+        <v>2173641.92753167</v>
       </c>
     </row>
     <row r="128">
@@ -3490,10 +3490,10 @@
         <v>500000</v>
       </c>
       <c r="E128" t="n">
-        <v>15770.77419189129</v>
+        <v>15770.77419172677</v>
       </c>
       <c r="F128" t="n">
-        <v>477413.9708310283</v>
+        <v>477413.9708258559</v>
       </c>
     </row>
     <row r="129">
@@ -3508,16 +3508,16 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D129" t="n">
         <v>101325</v>
       </c>
       <c r="E129" t="n">
-        <v>138989.0579301962</v>
+        <v>138989.1357119859</v>
       </c>
       <c r="F129" t="n">
-        <v>2537376.333549568</v>
+        <v>2537377.697521132</v>
       </c>
     </row>
     <row r="130">
@@ -3532,16 +3532,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D130" t="n">
         <v>101325</v>
       </c>
       <c r="E130" t="n">
-        <v>137623.6000916889</v>
+        <v>137623.6770617348</v>
       </c>
       <c r="F130" t="n">
-        <v>2513517.064955806</v>
+        <v>2513518.415476788</v>
       </c>
     </row>
     <row r="131">
@@ -3556,16 +3556,16 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D131" t="n">
         <v>101325</v>
       </c>
       <c r="E131" t="n">
-        <v>20001.27617717589</v>
+        <v>20001.28736882766</v>
       </c>
       <c r="F131" t="n">
-        <v>364968.1340713794</v>
+        <v>364968.3304424401</v>
       </c>
     </row>
     <row r="132">
@@ -3580,16 +3580,16 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D132" t="n">
         <v>101325</v>
       </c>
       <c r="E132" t="n">
-        <v>117622.323914513</v>
+        <v>117622.3896929071</v>
       </c>
       <c r="F132" t="n">
-        <v>2148548.930884426</v>
+        <v>2148550.085034348</v>
       </c>
     </row>
     <row r="133">
@@ -3604,16 +3604,16 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D133" t="n">
         <v>101325</v>
       </c>
       <c r="E133" t="n">
-        <v>112917.4309579325</v>
+        <v>112917.4941051908</v>
       </c>
       <c r="F133" t="n">
-        <v>2062606.97364905</v>
+        <v>2062608.081632973</v>
       </c>
     </row>
     <row r="134">
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D134" t="n">
         <v>101325</v>
       </c>
       <c r="E134" t="n">
-        <v>4704.892956580517</v>
+        <v>4704.895587716291</v>
       </c>
       <c r="F134" t="n">
-        <v>85941.95723537706</v>
+        <v>85942.00340137407</v>
       </c>
     </row>
     <row r="135">
@@ -3652,16 +3652,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>308.0440323356887</v>
+        <v>308.0440322610079</v>
       </c>
       <c r="D135" t="n">
         <v>101325</v>
       </c>
       <c r="E135" t="n">
-        <v>6257.10700066868</v>
+        <v>6257.105038319888</v>
       </c>
       <c r="F135" t="n">
-        <v>114145.7287317287</v>
+        <v>114145.6920326206</v>
       </c>
     </row>
     <row r="136">
@@ -3676,16 +3676,16 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>308.0440323356887</v>
+        <v>308.0440322610079</v>
       </c>
       <c r="D136" t="n">
         <v>101325</v>
       </c>
       <c r="E136" t="n">
-        <v>6087.918140859637</v>
+        <v>6087.916290195157</v>
       </c>
       <c r="F136" t="n">
-        <v>111033.8804359737</v>
+        <v>111033.8458986963</v>
       </c>
     </row>
     <row r="137">
@@ -3748,16 +3748,16 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>320.0000000000001</v>
+        <v>320.0000000000002</v>
       </c>
       <c r="D139" t="n">
         <v>500000</v>
       </c>
       <c r="E139" t="n">
-        <v>1961.844974056287</v>
+        <v>1961.844976303769</v>
       </c>
       <c r="F139" t="n">
-        <v>10399.85751874083</v>
+        <v>10399.85755740996</v>
       </c>
     </row>
     <row r="140">
@@ -3796,16 +3796,16 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>386.84602910017</v>
+        <v>386.8460291001701</v>
       </c>
       <c r="D141" t="n">
         <v>162120</v>
       </c>
       <c r="E141" t="n">
-        <v>1165.518200772243</v>
+        <v>1165.518200775619</v>
       </c>
       <c r="F141" t="n">
-        <v>20997.26459481816</v>
+        <v>20997.26459487898</v>
       </c>
     </row>
     <row r="142">
@@ -3820,16 +3820,16 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>308.0094028748006</v>
+        <v>308.0094028973302</v>
       </c>
       <c r="D142" t="n">
         <v>101325</v>
       </c>
       <c r="E142" t="n">
-        <v>19613.71562825187</v>
+        <v>19613.7269109447</v>
       </c>
       <c r="F142" t="n">
-        <v>353346.5788833334</v>
+        <v>353346.7821442038</v>
       </c>
     </row>
     <row r="143">
@@ -3850,10 +3850,10 @@
         <v>101325</v>
       </c>
       <c r="E143" t="n">
-        <v>3194.644592628149</v>
+        <v>3194.634179322498</v>
       </c>
       <c r="F143" t="n">
-        <v>57552.41683668203</v>
+        <v>57552.22923806501</v>
       </c>
     </row>
     <row r="144">
@@ -3874,10 +3874,10 @@
         <v>101325</v>
       </c>
       <c r="E144" t="n">
-        <v>19541.03823226556</v>
+        <v>19540.97313750136</v>
       </c>
       <c r="F144" t="n">
-        <v>352037.2752449691</v>
+        <v>352036.1025445656</v>
       </c>
     </row>
     <row r="145">
@@ -3922,10 +3922,10 @@
         <v>101325</v>
       </c>
       <c r="E146" t="n">
-        <v>6826.604027045992</v>
+        <v>6826.538929858031</v>
       </c>
       <c r="F146" t="n">
-        <v>122983.1829963611</v>
+        <v>122982.0102522928</v>
       </c>
     </row>
     <row r="147">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>308.0440323356887</v>
+        <v>308.0440322610079</v>
       </c>
       <c r="D147" t="n">
         <v>101325</v>
       </c>
       <c r="E147" t="n">
-        <v>169.188859809043</v>
+        <v>169.1887481247298</v>
       </c>
       <c r="F147" t="n">
-        <v>3111.84829575499</v>
+        <v>3111.846133924334</v>
       </c>
     </row>
     <row r="148">
@@ -3970,7 +3970,7 @@
         <v>101325</v>
       </c>
       <c r="E148" t="n">
-        <v>19819.25267196402</v>
+        <v>19819.25232762429</v>
       </c>
       <c r="F148" t="n">
         <v>391160.1294498382</v>
@@ -3988,16 +3988,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>314.6565436477393</v>
+        <v>314.6565436414825</v>
       </c>
       <c r="D149" t="n">
         <v>607950</v>
       </c>
       <c r="E149" t="n">
-        <v>19772.74432546267</v>
+        <v>19772.74436431224</v>
       </c>
       <c r="F149" t="n">
-        <v>356294.6228401382</v>
+        <v>356294.6228345982</v>
       </c>
     </row>
     <row r="150">
@@ -4018,10 +4018,10 @@
         <v>101325</v>
       </c>
       <c r="E150" t="n">
-        <v>1450.076802032194</v>
+        <v>1450.076804455962</v>
       </c>
       <c r="F150" t="n">
-        <v>26123.53961011455</v>
+        <v>26123.5396537794</v>
       </c>
     </row>
     <row r="151">
@@ -4060,16 +4060,16 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>313.3253459890073</v>
+        <v>313.3253467515595</v>
       </c>
       <c r="D152" t="n">
         <v>101325</v>
       </c>
       <c r="E152" t="n">
-        <v>1647.250059877784</v>
+        <v>1647.249946944121</v>
       </c>
       <c r="F152" t="n">
-        <v>22823.04853061022</v>
+        <v>22823.04632108148</v>
       </c>
     </row>
     <row r="153">
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>304.5064465817767</v>
+        <v>304.5064465829527</v>
       </c>
       <c r="D153" t="n">
         <v>101325</v>
       </c>
       <c r="E153" t="n">
-        <v>458.2270968181729</v>
+        <v>458.2270968218999</v>
       </c>
       <c r="F153" t="n">
-        <v>20109.25178793738</v>
+        <v>20109.25178800085</v>
       </c>
     </row>
     <row r="154">
